--- a/Software Testing Fundamentals/Testing sheet.xlsx
+++ b/Software Testing Fundamentals/Testing sheet.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\SkillsRepository\Software Testing Fundamentals\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DC28CB7-D600-4247-A4C2-7521E3118AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7B03C43-ABC1-4158-8E04-66472F1DBAD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Calculator.java" sheetId="1" r:id="rId1"/>
+    <sheet name="Calculator.java" sheetId="3" r:id="rId1"/>
+    <sheet name="Calculator.java devided by zero" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="15">
   <si>
     <t>+</t>
   </si>
@@ -64,6 +65,12 @@
   </si>
   <si>
     <t>✅</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>Error</t>
   </si>
 </sst>
 </file>
@@ -188,7 +195,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -482,8 +489,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{972B146B-91B6-4A36-B8A6-C3540648D2C8}">
+  <dimension ref="B2:G8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.77734375" customWidth="1"/>
@@ -595,6 +602,155 @@
         <v>12</v>
       </c>
     </row>
+    <row r="8" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="1">
+        <v>10</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B2:G8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="18.77734375" customWidth="1"/>
+    <col min="3" max="3" width="15.5546875" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" customWidth="1"/>
+    <col min="5" max="5" width="21" customWidth="1"/>
+    <col min="7" max="7" width="21.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" ht="42.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="1">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1">
+        <v>5</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="1">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1">
+        <v>4</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1">
+        <v>6</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="1">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="1">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1">
+        <v>9</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="1">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="1">
+        <v>10</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Software Testing Fundamentals/Testing sheet.xlsx
+++ b/Software Testing Fundamentals/Testing sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\SkillsRepository\Software Testing Fundamentals\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7B03C43-ABC1-4158-8E04-66472F1DBAD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD9CEB2B-2D03-4199-9086-0B6955F2156C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Calculator.java" sheetId="3" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="16">
   <si>
     <t>+</t>
   </si>
@@ -58,9 +58,6 @@
     <t>Uknowb operator</t>
   </si>
   <si>
-    <t>checklist</t>
-  </si>
-  <si>
     <t>❌</t>
   </si>
   <si>
@@ -71,6 +68,12 @@
   </si>
   <si>
     <t>Error</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>checklist / pass</t>
   </si>
 </sst>
 </file>
@@ -95,7 +98,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -114,6 +117,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -187,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -198,16 +207,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -490,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{972B146B-91B6-4A36-B8A6-C3540648D2C8}">
-  <dimension ref="B2:G8"/>
+  <dimension ref="B2:K8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.77734375" customWidth="1"/>
@@ -500,12 +512,12 @@
     <col min="7" max="7" width="21.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="42.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:11" ht="42" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>6</v>
@@ -514,10 +526,10 @@
         <v>7</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1">
         <v>2</v>
       </c>
@@ -530,11 +542,9 @@
       <c r="E3" s="1">
         <v>5</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G3" s="7"/>
+    </row>
+    <row r="4" spans="2:11" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
         <v>10</v>
       </c>
@@ -547,11 +557,12 @@
       <c r="E4" s="1">
         <v>6</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G4" s="7"/>
+      <c r="K4" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <v>5</v>
       </c>
@@ -564,11 +575,12 @@
       <c r="E5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G5" s="7"/>
+      <c r="K5" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <v>3</v>
       </c>
@@ -581,11 +593,9 @@
       <c r="E6" s="1">
         <v>9</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G6" s="7"/>
+    </row>
+    <row r="7" spans="2:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <v>5</v>
       </c>
@@ -598,24 +608,20 @@
       <c r="E7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G7" s="7"/>
+    </row>
+    <row r="8" spans="2:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
         <v>10</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>12</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G8" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -624,7 +630,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G8"/>
+  <dimension ref="B2:K8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.77734375" customWidth="1"/>
@@ -634,12 +640,12 @@
     <col min="7" max="7" width="21.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="42.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:11" ht="42.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>6</v>
@@ -648,10 +654,10 @@
         <v>7</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1">
         <v>2</v>
       </c>
@@ -664,11 +670,9 @@
       <c r="E3" s="1">
         <v>5</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G3" s="6"/>
+    </row>
+    <row r="4" spans="2:11" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
         <v>10</v>
       </c>
@@ -681,11 +685,12 @@
       <c r="E4" s="1">
         <v>6</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G4" s="7"/>
+      <c r="K4" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <v>5</v>
       </c>
@@ -698,11 +703,12 @@
       <c r="E5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G5" s="7"/>
+      <c r="K5" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <v>3</v>
       </c>
@@ -715,11 +721,9 @@
       <c r="E6" s="1">
         <v>9</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G6" s="7"/>
+    </row>
+    <row r="7" spans="2:11" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="1">
         <v>5</v>
       </c>
@@ -732,24 +736,20 @@
       <c r="E7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G7" s="8"/>
+    </row>
+    <row r="8" spans="2:11" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="1">
         <v>10</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>12</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G8" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Software Testing Fundamentals/Testing sheet.xlsx
+++ b/Software Testing Fundamentals/Testing sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\SkillsRepository\Software Testing Fundamentals\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7B03C43-ABC1-4158-8E04-66472F1DBAD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AABD8BDF-2E56-465E-90A3-DEED30DBD3E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="16">
   <si>
     <t>+</t>
   </si>
@@ -71,6 +71,9 @@
   </si>
   <si>
     <t>Error</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
 </sst>
 </file>
@@ -505,7 +508,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>6</v>
@@ -639,7 +642,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>6</v>
